--- a/files/UAE_010_ФПЗ_ПРЕДВАРИТЕЛЬНЫЙ_23.06.2026.xlsx
+++ b/files/UAE_010_ФПЗ_ПРЕДВАРИТЕЛЬНЫЙ_23.06.2026.xlsx
@@ -5,18 +5,19 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\001 UAE\UAE#10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\001 UAE\UAE#10_APMG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362EB6C7-1FF0-48E7-8151-8DD0DE541944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623B464A-1F11-4B41-8E72-C2F6C469F152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="2460" windowWidth="35295" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="1830" windowWidth="35295" windowHeight="18060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ФПЗ_Э10" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="57">
   <si>
     <t>Производитель</t>
   </si>
@@ -469,7 +470,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -676,6 +677,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="11" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2042,7 +2060,7 @@
       <c r="AMK1" s="22"/>
     </row>
     <row r="2" spans="1:1025" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="23" t="s">
@@ -3141,7 +3159,7 @@
       <c r="AMK2" s="22"/>
     </row>
     <row r="3" spans="1:1025" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="76" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="23" t="s">
@@ -4241,7 +4259,7 @@
       <c r="AMK3" s="22"/>
     </row>
     <row r="4" spans="1:1025" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="76" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="23" t="s">
@@ -5341,7 +5359,7 @@
       <c r="AMK4" s="22"/>
     </row>
     <row r="5" spans="1:1025" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="76" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="23" t="s">
@@ -6443,32 +6461,32 @@
       <c r="A6" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="79">
         <v>1</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="79">
         <v>1152</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="79">
         <f t="shared" si="9"/>
         <v>1152</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25">
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79">
         <v>12</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="79">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="80">
         <v>6.9</v>
       </c>
       <c r="L6" s="26">
@@ -6545,7 +6563,7 @@
       <c r="AE6" s="21"/>
     </row>
     <row r="7" spans="1:1025" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="76" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="58" t="s">
@@ -6654,32 +6672,32 @@
       <c r="A8" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="79">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="79">
         <v>120</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="79">
         <f t="shared" si="9"/>
         <v>120</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25">
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79">
         <v>12</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="79">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="80">
         <v>6.8</v>
       </c>
       <c r="L8" s="26">
@@ -6756,7 +6774,7 @@
       <c r="AE8" s="21"/>
     </row>
     <row r="9" spans="1:1025" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="76" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="73" t="s">
@@ -6861,7 +6879,7 @@
       <c r="AE9" s="21"/>
     </row>
     <row r="10" spans="1:1025" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="76" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="68" t="s">
@@ -6966,7 +6984,7 @@
       <c r="AE10" s="21"/>
     </row>
     <row r="11" spans="1:1025" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="76" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="68" t="s">
@@ -7071,7 +7089,7 @@
       <c r="AE11" s="21"/>
     </row>
     <row r="12" spans="1:1025" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="76" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="68" t="s">
@@ -7170,7 +7188,7 @@
       <c r="AE12" s="21"/>
     </row>
     <row r="13" spans="1:1025" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="76" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="68" t="s">
@@ -7667,6 +7685,491 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2079867-FC2F-454A-AACC-14526432C298}">
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultColWidth="32.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="103.42578125" customWidth="1"/>
+    <col min="6" max="8" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="25">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25">
+        <v>720</v>
+      </c>
+      <c r="F2" s="25">
+        <f>E2*D2</f>
+        <v>720</v>
+      </c>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25">
+        <v>12</v>
+      </c>
+      <c r="J2" s="25">
+        <f>E2/I2</f>
+        <v>60</v>
+      </c>
+      <c r="L2" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2">
+        <f>SUMIF($A$2:$A$13,L2,$E$2:$E$13)</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="25">
+        <v>5</v>
+      </c>
+      <c r="E3" s="25">
+        <f>720-240-120</f>
+        <v>360</v>
+      </c>
+      <c r="F3" s="25">
+        <f t="shared" ref="F3:F10" si="0">E3*D3</f>
+        <v>1800</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25">
+        <v>3</v>
+      </c>
+      <c r="J3" s="25">
+        <f t="shared" ref="J3:J13" si="1">E3/I3</f>
+        <v>120</v>
+      </c>
+      <c r="L3" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M11" si="2">SUMIF($A$2:$A$13,L3,$E$2:$E$13)</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="25">
+        <v>5</v>
+      </c>
+      <c r="E4" s="25">
+        <f>720-120</f>
+        <v>600</v>
+      </c>
+      <c r="F4" s="25">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25">
+        <v>3</v>
+      </c>
+      <c r="J4" s="25">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L4" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="25">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25">
+        <v>720</v>
+      </c>
+      <c r="F5" s="25">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25">
+        <v>12</v>
+      </c>
+      <c r="J5" s="25">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="L5" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="79">
+        <v>1</v>
+      </c>
+      <c r="E6" s="79">
+        <v>1152</v>
+      </c>
+      <c r="F6" s="79">
+        <f t="shared" si="0"/>
+        <v>1152</v>
+      </c>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79">
+        <v>12</v>
+      </c>
+      <c r="J6" s="79">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="L6" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="25">
+        <v>4</v>
+      </c>
+      <c r="E7" s="25">
+        <f>144*10</f>
+        <v>1440</v>
+      </c>
+      <c r="F7" s="25">
+        <f t="shared" si="0"/>
+        <v>5760</v>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25">
+        <v>3</v>
+      </c>
+      <c r="J7" s="25">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="L7" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="79">
+        <v>1</v>
+      </c>
+      <c r="E8" s="79">
+        <v>120</v>
+      </c>
+      <c r="F8" s="79">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79">
+        <v>12</v>
+      </c>
+      <c r="J8" s="79">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L8" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="25">
+        <v>5</v>
+      </c>
+      <c r="E9" s="25">
+        <v>240</v>
+      </c>
+      <c r="F9" s="25">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25">
+        <v>3</v>
+      </c>
+      <c r="J9" s="25">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="L9" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>632</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="70">
+        <v>1</v>
+      </c>
+      <c r="E10" s="25">
+        <v>5760</v>
+      </c>
+      <c r="F10" s="25">
+        <f t="shared" si="0"/>
+        <v>5760</v>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25">
+        <v>12</v>
+      </c>
+      <c r="J10" s="25">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="L10" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="70">
+        <v>4</v>
+      </c>
+      <c r="E11" s="25">
+        <v>632</v>
+      </c>
+      <c r="F11" s="25">
+        <f>E11*D11</f>
+        <v>2528</v>
+      </c>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25">
+        <v>4</v>
+      </c>
+      <c r="J11" s="25">
+        <f t="shared" si="1"/>
+        <v>158</v>
+      </c>
+      <c r="L11" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="70">
+        <v>1</v>
+      </c>
+      <c r="E12" s="25">
+        <v>1440</v>
+      </c>
+      <c r="F12" s="25">
+        <f>E12*D12</f>
+        <v>1440</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25">
+        <v>12</v>
+      </c>
+      <c r="J12" s="25">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="70">
+        <v>1</v>
+      </c>
+      <c r="E13" s="25">
+        <v>336</v>
+      </c>
+      <c r="F13" s="25">
+        <f>E13*D13</f>
+        <v>336</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25">
+        <v>12</v>
+      </c>
+      <c r="J13" s="25">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J14" s="81">
+        <f>SUM(J2:J13)</f>
+        <v>1892</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E1C031C-34C6-4693-8808-CB575DA1DE33}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="34.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -7724,7 +8227,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="25">
-        <f>E2/G2</f>
+        <f t="shared" ref="H2:H13" si="0">E2/G2</f>
         <v>60</v>
       </c>
       <c r="I2" s="26">
@@ -7753,21 +8256,21 @@
         <v>360</v>
       </c>
       <c r="F3" s="25">
-        <f t="shared" ref="F3:F10" si="0">E3*D3</f>
+        <f t="shared" ref="F3:F10" si="1">E3*D3</f>
         <v>1800</v>
       </c>
       <c r="G3" s="25">
         <v>3</v>
       </c>
       <c r="H3" s="25">
-        <f>E3/G3</f>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="I3" s="26">
         <v>35.93</v>
       </c>
       <c r="J3" s="75">
-        <f t="shared" ref="J3:J13" si="1">I3*3.67</f>
+        <f t="shared" ref="J3:J13" si="2">I3*3.67</f>
         <v>131.8631</v>
       </c>
     </row>
@@ -7789,21 +8292,21 @@
         <v>600</v>
       </c>
       <c r="F4" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3000</v>
       </c>
       <c r="G4" s="25">
         <v>3</v>
       </c>
       <c r="H4" s="25">
-        <f>E4/G4</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="I4" s="26">
         <v>28.94</v>
       </c>
       <c r="J4" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>106.2098</v>
       </c>
     </row>
@@ -7824,21 +8327,21 @@
         <v>720</v>
       </c>
       <c r="F5" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>720</v>
       </c>
       <c r="G5" s="25">
         <v>12</v>
       </c>
       <c r="H5" s="25">
-        <f>E5/G5</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="I5" s="26">
         <v>5.99</v>
       </c>
       <c r="J5" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21.9833</v>
       </c>
     </row>
@@ -7859,21 +8362,21 @@
         <v>1152</v>
       </c>
       <c r="F6" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1152</v>
       </c>
       <c r="G6" s="25">
         <v>12</v>
       </c>
       <c r="H6" s="25">
-        <f>E6/G6</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="I6" s="26">
         <v>6.9</v>
       </c>
       <c r="J6" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25.323</v>
       </c>
     </row>
@@ -7895,21 +8398,21 @@
         <v>1440</v>
       </c>
       <c r="F7" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5760</v>
       </c>
       <c r="G7" s="25">
         <v>3</v>
       </c>
       <c r="H7" s="25">
-        <f>E7/G7</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="I7" s="26">
         <v>15.41</v>
       </c>
       <c r="J7" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>56.554699999999997</v>
       </c>
     </row>
@@ -7930,21 +8433,21 @@
         <v>120</v>
       </c>
       <c r="F8" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="G8" s="25">
         <v>12</v>
       </c>
       <c r="H8" s="25">
-        <f>E8/G8</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I8" s="26">
         <v>6.8</v>
       </c>
       <c r="J8" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24.956</v>
       </c>
     </row>
@@ -7965,21 +8468,21 @@
         <v>240</v>
       </c>
       <c r="F9" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="G9" s="25">
         <v>3</v>
       </c>
       <c r="H9" s="25">
-        <f>E9/G9</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="I9" s="26">
         <v>35.44</v>
       </c>
       <c r="J9" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>130.06479999999999</v>
       </c>
     </row>
@@ -8000,21 +8503,21 @@
         <v>5760</v>
       </c>
       <c r="F10" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5760</v>
       </c>
       <c r="G10" s="25">
         <v>12</v>
       </c>
       <c r="H10" s="25">
-        <f>E10/G10</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="I10" s="26">
         <v>8.6</v>
       </c>
       <c r="J10" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31.561999999999998</v>
       </c>
     </row>
@@ -8042,14 +8545,14 @@
         <v>4</v>
       </c>
       <c r="H11" s="25">
-        <f>E11/G11</f>
+        <f t="shared" si="0"/>
         <v>158</v>
       </c>
       <c r="I11" s="26">
         <v>25</v>
       </c>
       <c r="J11" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>91.75</v>
       </c>
     </row>
@@ -8077,14 +8580,14 @@
         <v>12</v>
       </c>
       <c r="H12" s="25">
-        <f>E12/G12</f>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="I12" s="26">
         <v>5.9</v>
       </c>
       <c r="J12" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21.653000000000002</v>
       </c>
     </row>
@@ -8112,14 +8615,14 @@
         <v>12</v>
       </c>
       <c r="H13" s="25">
-        <f>E13/G13</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I13" s="26">
         <v>4.5</v>
       </c>
       <c r="J13" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.515000000000001</v>
       </c>
     </row>

--- a/files/UAE_010_ФПЗ_ПРЕДВАРИТЕЛЬНЫЙ_23.06.2026.xlsx
+++ b/files/UAE_010_ФПЗ_ПРЕДВАРИТЕЛЬНЫЙ_23.06.2026.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\001 UAE\UAE#10_APMG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623B464A-1F11-4B41-8E72-C2F6C469F152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81604AFD-FAB8-41EF-92E7-0DD0F5D90ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="1830" windowWidth="35295" windowHeight="18060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="35295" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ФПЗ_Э10" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
